--- a/mode_docx_gen/pmi_ka2/ka_modes/КА_27.xlsx
+++ b/mode_docx_gen/pmi_ka2/ka_modes/КА_27.xlsx
@@ -647,8 +647,8 @@
       <c r="N2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>1</v>
+      <c r="O2" t="n">
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>1</v>
@@ -1185,8 +1185,8 @@
       <c r="AB2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC2" s="2" t="n">
-        <v>1</v>
+      <c r="AC2" t="n">
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -1497,9 +1497,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1507,14 +1507,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1657,19 +1657,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AI2" s="2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
